--- a/Zoomlion/ZA18J.xlsx
+++ b/Zoomlion/ZA18J.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,36 +413,36 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F544"/>
+  <dimension ref="A1:F542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Код материалов</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Кол-во</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Наименование и спецификация</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Примечание</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Section</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Models</t>
         </is>
@@ -8535,7 +8523,7 @@
         </is>
       </c>
       <c r="B312" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
@@ -8545,7 +8533,7 @@
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -8851,21 +8839,21 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1020509007</t>
+          <t>1020516032</t>
         </is>
       </c>
       <c r="B324" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Кнопочная станция</t>
+          <t>Концевой выключатель угла поворотной платформы; Концевой выключатель длины стрелы 2; Концевой выключатель длины стрелы 1; Концевой выключатель угла башенной стрелы 2; Концевой выключатель угла башенной стрелы 1</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Пучок кабеля поворотной платформы 00773606200410000; Пучок кабеля стрелы 00773606200430000</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -8877,21 +8865,25 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1020516032</t>
+          <t>1020519658</t>
         </is>
       </c>
       <c r="B325" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Концевой выключатель угла поворотной платформы; Концевой выключатель длины стрелы 2; Концевой выключатель длины стрелы 1; Концевой выключатель угла башенной стрелы 2; Концевой выключатель угла башенной стрелы 1</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr"/>
+          <t>Кнопка аварийной остановки</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Аварийный выключатель</t>
+        </is>
+      </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773606200410000; Пучок кабеля стрелы 00773606200430000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -8903,20 +8895,20 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1020519658</t>
+          <t>1020520084</t>
         </is>
       </c>
       <c r="B326" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Кнопка аварийной остановки</t>
+          <t>Рычажный переключатель</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Аварийный выключатель</t>
+          <t>Переключатель вращения платформы; Переключатель подъема-опускания консоли; Выдвижение- втягивание стрелы; Подъем-опускание башенной стрелы; Вращение платформы; Выравнивание платформы; Подъем-опускание консоли; Подъем-опускание стрелы; Вращение поворотной платформы; Аварийное энергопитание и активация</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -8933,25 +8925,21 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>1020520084</t>
+          <t>1020520943</t>
         </is>
       </c>
       <c r="B327" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Рычажный переключатель</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>Переключатель вращения платформы; Переключатель подъема-опускания консоли; Выдвижение- втягивание стрелы; Подъем-опускание башенной стрелы; Вращение платформы; Выравнивание платформы; Подъем-опускание консоли; Подъем-опускание стрелы; Вращение поворотной платформы; Аварийное энергопитание и активация</t>
-        </is>
-      </c>
+          <t>Переключатель с ключом</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -8963,7 +8951,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>1020520943</t>
+          <t>1020520993</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -8971,13 +8959,13 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Переключатель с ключом</t>
+          <t>Рычаг</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -8989,7 +8977,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>1020520993</t>
+          <t>1020520994</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -9015,7 +9003,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>1020520994</t>
+          <t>1020520995</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -9023,7 +9011,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>Рычаг</t>
+          <t>Потенциометр</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -9041,21 +9029,21 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>1020520995</t>
+          <t>1020521022</t>
         </is>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Потенциометр</t>
+          <t>Педальный переключатель</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Пучок кабеля платформы 00773606200440000 Модификация волочащегося кабеля 00773606200610000</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -9067,21 +9055,25 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>1020521022</t>
+          <t>1020521443</t>
         </is>
       </c>
       <c r="B332" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Педальный переключатель</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr"/>
+          <t>Качающийся переключатель</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Управление скоростью хода</t>
+        </is>
+      </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Пучок кабеля платформы 00773606200440000 Модификация волочащегося кабеля 00773606200610000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -9093,7 +9085,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>1020521443</t>
+          <t>1020521444</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -9106,7 +9098,7 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Управление скоростью хода</t>
+          <t>Освещение</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -9123,7 +9115,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>1020521444</t>
+          <t>1020521445</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -9136,7 +9128,7 @@
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Освещение</t>
+          <t>Выравнивание платформы</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -9153,25 +9145,21 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>1020521445</t>
+          <t>1020604934</t>
         </is>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Качающийся переключатель</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>Выравнивание платформы</t>
-        </is>
-      </c>
+          <t>Соединительный зажим</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr"/>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -9183,21 +9171,21 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1020604934</t>
+          <t>1020605356</t>
         </is>
       </c>
       <c r="B336" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Соединительный зажим</t>
+          <t>Кольцевой предохранитель</t>
         </is>
       </c>
       <c r="D336" t="inlineStr"/>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Питательный провод 00773606200450000</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -9209,21 +9197,21 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>1020605356</t>
+          <t>1020605390</t>
         </is>
       </c>
       <c r="B337" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Кольцевой предохранитель</t>
+          <t>Пневматическая пружина</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Питательный провод 00773606200450000</t>
+          <t>Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -9235,7 +9223,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>1020605390</t>
+          <t>1020703393</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -9243,13 +9231,17 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Пневматическая пружина</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr"/>
+          <t>Круглый разъем</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Пучок кабеля платформы</t>
+        </is>
+      </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -9261,7 +9253,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>1020703393</t>
+          <t>1020703394</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -9269,12 +9261,12 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Круглый разъем</t>
+          <t>Соединитель DEUTSCH</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>Пучок кабеля платформы</t>
+          <t>Пучок волочащегося кабеля</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
@@ -9291,25 +9283,21 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>1020703394</t>
+          <t>1020704265</t>
         </is>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Соединитель DEUTSCH</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>Пучок волочащегося кабеля</t>
-        </is>
-      </c>
+          <t>Клеммная колодка заземления</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr"/>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -9321,15 +9309,15 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1020704265</t>
+          <t>1020705826</t>
         </is>
       </c>
       <c r="B341" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Клеммная колодка заземления</t>
+          <t>Зажим диода</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -9347,7 +9335,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1020705826</t>
+          <t>1020810958</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -9355,13 +9343,17 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Зажим диода</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr"/>
+          <t>Качающийся переключатель</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Аварийное энергопитание и активация; Ориентация привода</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -9373,25 +9365,21 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1020810958</t>
+          <t>1021404016</t>
         </is>
       </c>
       <c r="B343" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Качающийся переключатель</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>Аварийное энергопитание и активация; Ориентация привода</t>
-        </is>
-      </c>
+          <t>Датчик веса</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr"/>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Пучок кабеля платформы 00773606200440000 Модификация волочащегося кабеля 00773606200610000</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -9403,21 +9391,21 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1021404016</t>
+          <t>1021404018</t>
         </is>
       </c>
       <c r="B344" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Датчик веса</t>
+          <t>Двухугольный датчик угла наклона</t>
         </is>
       </c>
       <c r="D344" t="inlineStr"/>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Пучок кабеля платформы 00773606200440000 Модификация волочащегося кабеля 00773606200610000</t>
+          <t>Пучок кабеля стрелы 00773606200430000</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -9429,7 +9417,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>1021404018</t>
+          <t>1021404019</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -9437,13 +9425,13 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Двухугольный датчик угла наклона</t>
+          <t>Датчик наклона кузова относительно горизонта</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Пучок кабеля стрелы 00773606200430000</t>
+          <t>Пучок кабеля поворотной платформы 00773606200410000</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -9455,7 +9443,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>1021404019</t>
+          <t>1022399012</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -9463,13 +9451,13 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Датчик наклона кузова относительно горизонта</t>
+          <t>Канал для электропроводки</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы 00773606200410000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -9481,15 +9469,15 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1022399012</t>
+          <t>1029802085</t>
         </is>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Канал для электропроводки</t>
+          <t>Нейлоновая заглушка</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -9507,21 +9495,21 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>1029802085</t>
+          <t>1029900667</t>
         </is>
       </c>
       <c r="B348" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Нейлоновая заглушка</t>
+          <t>Ручной переключатель</t>
         </is>
       </c>
       <c r="D348" t="inlineStr"/>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Питательный провод 00773606200450000</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -9533,21 +9521,25 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>1029804205</t>
+          <t>1029902634</t>
         </is>
       </c>
       <c r="B349" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Затяжная гайка</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr"/>
+          <t>32-жильный кабель в оболочке</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Пучок кабеля поворотной платформы; Пучок кабеля стрелы</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -9559,7 +9551,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>1029900667</t>
+          <t>1029903317</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -9567,13 +9559,17 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Ручной переключатель</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr"/>
+          <t>48-жильный кабель в оболочке</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Пучок кабеля поворотной платформы</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Питательный провод 00773606200450000</t>
+          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -9585,25 +9581,25 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>1029902634</t>
+          <t>1029904911</t>
         </is>
       </c>
       <c r="B351" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>32-жильный кабель в оболочке</t>
+          <t>Пружинная подстилка 5</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Пучок кабеля поворотной платформы; Пучок кабеля стрелы</t>
+          <t>GB93; JB/T93</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -9615,25 +9611,21 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>1029903317</t>
+          <t>1029904980</t>
         </is>
       </c>
       <c r="B352" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>48-жильный кабель в оболочке</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>Пучок кабеля поворотной платформы</t>
-        </is>
-      </c>
+          <t>Зажим; Соединительный зажим</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr"/>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -9645,25 +9637,21 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>1029904911</t>
+          <t>1029905348</t>
         </is>
       </c>
       <c r="B353" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Пружинная подстилка 5</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>GB93; JB/T93</t>
-        </is>
-      </c>
+          <t>Аккумулятор</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr"/>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Питательный провод 00773606200450000</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -9675,21 +9663,21 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1029904980</t>
+          <t>1029905392</t>
         </is>
       </c>
       <c r="B354" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Зажим; Соединительный зажим</t>
+          <t>Зажим</t>
         </is>
       </c>
       <c r="D354" t="inlineStr"/>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000; Электрический шкаф управления поворотной платформой в сборе 00773706200220000</t>
+          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -9701,21 +9689,21 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>1029905348</t>
+          <t>1030202174</t>
         </is>
       </c>
       <c r="B355" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Аккумулятор</t>
+          <t>Редуктор</t>
         </is>
       </c>
       <c r="D355" t="inlineStr"/>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Питательный провод 00773606200450000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -9727,21 +9715,21 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>1029905392</t>
+          <t>1030202348</t>
         </is>
       </c>
       <c r="B356" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Зажим</t>
+          <t>Поворотный редуктор</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Электрический шкаф управления платформой в сборе 00773406200210000</t>
+          <t>Поворотный механизм 00773700900000000</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -9753,15 +9741,15 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>1030202174</t>
+          <t>1030800662</t>
         </is>
       </c>
       <c r="B357" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Редуктор</t>
+          <t>Шина 355/55D-625(L)-OTR</t>
         </is>
       </c>
       <c r="D357" t="inlineStr"/>
@@ -9779,21 +9767,21 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>1030202348</t>
+          <t>1030800663</t>
         </is>
       </c>
       <c r="B358" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Поворотный редуктор</t>
+          <t>Шина 355/55D-625(R)-OTR</t>
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Поворотный механизм 00773700900000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -9805,21 +9793,25 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1030800662</t>
+          <t>1040000135</t>
         </is>
       </c>
       <c r="B359" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Шина 355/55D-625(L)-OTR</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr"/>
+          <t>Болт M8×55</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>JB/T5783</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -9831,7 +9823,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1030800663</t>
+          <t>1040001029</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -9839,13 +9831,17 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Шина 355/55D-625(R)-OTR</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr"/>
+          <t>Винт M12×35-10.9</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>JB/T5783</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -9857,15 +9853,15 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1040000135</t>
+          <t>1040001631</t>
         </is>
       </c>
       <c r="B361" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Болт M8×55</t>
+          <t>Болт M6×20-A2-70; Болт M6×20</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -9875,7 +9871,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -9887,15 +9883,15 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1040001029</t>
+          <t>1040001640</t>
         </is>
       </c>
       <c r="B362" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Винт M12×35-10.9</t>
+          <t>Болт M6×25-A2-70</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -9905,7 +9901,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000</t>
+          <t>Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -9917,15 +9913,15 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1040001631</t>
+          <t>1040002262</t>
         </is>
       </c>
       <c r="B363" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Болт M6×20-A2-70; Болт M6×20</t>
+          <t>Болт</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -9935,7 +9931,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000</t>
+          <t>Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -9947,25 +9943,25 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1040001640</t>
+          <t>1040002273</t>
         </is>
       </c>
       <c r="B364" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Болт M6×25-A2-70</t>
+          <t>Болт</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5786</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -9977,15 +9973,15 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1040002262</t>
+          <t>1040002433</t>
         </is>
       </c>
       <c r="B365" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Болт</t>
+          <t>Болт M10×20-8.8</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -9995,7 +9991,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Cистема отвода тепла 00773607100600000</t>
+          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -10007,25 +10003,25 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1040002273</t>
+          <t>1040002434</t>
         </is>
       </c>
       <c r="B366" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Болт</t>
+          <t>Болт M10×25-8.8; Болт</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>JB/T5786</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
@@ -10037,15 +10033,15 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1040002433</t>
+          <t>1040002435</t>
         </is>
       </c>
       <c r="B367" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Болт M10×20-8.8</t>
+          <t>Болт M10×35-8.8</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -10055,7 +10051,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
@@ -10067,15 +10063,15 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>1040002434</t>
+          <t>1040002436</t>
         </is>
       </c>
       <c r="B368" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Болт M10×25-8.8; Болт</t>
+          <t>Болт M12×25-8,8</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -10085,7 +10081,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Cистема топлива 00773607100400000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
@@ -10097,15 +10093,15 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1040002435</t>
+          <t>1040002437</t>
         </is>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Болт M10×35-8.8</t>
+          <t>Болт M12×35-8,8</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -10115,7 +10111,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
@@ -10127,15 +10123,15 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1040002436</t>
+          <t>1040002445</t>
         </is>
       </c>
       <c r="B370" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Болт M12×25-8,8</t>
+          <t>Болт M16×35-8,8; Болт M16×35-8.8</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -10145,7 +10141,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -10157,15 +10153,15 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>1040002437</t>
+          <t>1040002446</t>
         </is>
       </c>
       <c r="B371" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Болт M12×35-8,8</t>
+          <t>Болт M16×40-8,8</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -10175,7 +10171,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -10187,15 +10183,15 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1040002445</t>
+          <t>1040002458</t>
         </is>
       </c>
       <c r="B372" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Болт M16×35-8,8; Болт M16×35-8.8</t>
+          <t>Болт M8×40-8,8</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -10205,7 +10201,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Капот 00773601100000000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
@@ -10217,15 +10213,15 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>1040002446</t>
+          <t>1040002555</t>
         </is>
       </c>
       <c r="B373" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Болт M16×40-8,8</t>
+          <t>Болт M6×16-A2-70; Болт; Винт M6×16-8.8</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -10235,7 +10231,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Шасси 00773602800000000</t>
+          <t>Поворотная платформа 00773600800000000; Шасси 00773602800000000; Главный клапан в сборе 00773605201600000</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
@@ -10247,15 +10243,15 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>1040002458</t>
+          <t>1040002738</t>
         </is>
       </c>
       <c r="B374" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Болт M8×40-8,8</t>
+          <t>Болт M6×12-A2-70</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -10265,7 +10261,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -10277,25 +10273,25 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>1040002555</t>
+          <t>1040003357</t>
         </is>
       </c>
       <c r="B375" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Болт M6×16-A2-70; Болт; Винт M6×16-8.8</t>
+          <t>Болт</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5786</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000; Шасси 00773602800000000; Главный клапан в сборе 00773605201600000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -10307,15 +10303,15 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>1040002738</t>
+          <t>1040003572</t>
         </is>
       </c>
       <c r="B376" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Болт M6×12-A2-70</t>
+          <t>Болт M16×55-10,9-DKL</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -10325,7 +10321,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -10337,25 +10333,25 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>1040003357</t>
+          <t>1040003720</t>
         </is>
       </c>
       <c r="B377" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Болт</t>
+          <t>Болт M10×20-8.8</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>JB/T5786</t>
+          <t>JB/T5787</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Сборка фильтра низкого давления 00773605201400000</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -10367,15 +10363,15 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>1040003572</t>
+          <t>1040003912</t>
         </is>
       </c>
       <c r="B378" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Болт M16×55-10,9-DKL</t>
+          <t>Болт</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -10385,7 +10381,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -10397,25 +10393,25 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>1040003720</t>
+          <t>1040004033</t>
         </is>
       </c>
       <c r="B379" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Болт M10×20-8.8</t>
+          <t>Болт M10×25-10.9</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>JB/T5787</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Сборка фильтра низкого давления 00773605201400000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -10427,15 +10423,15 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1040003912</t>
+          <t>1040004499</t>
         </is>
       </c>
       <c r="B380" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Болт</t>
+          <t>Болт M20×45-8,8</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -10445,7 +10441,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
@@ -10457,20 +10453,20 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1040004033</t>
+          <t>1040004505</t>
         </is>
       </c>
       <c r="B381" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Болт M10×25-10.9</t>
+          <t>Болт M24×280-10,9</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5782</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
@@ -10487,15 +10483,15 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>1040004499</t>
+          <t>1040004508</t>
         </is>
       </c>
       <c r="B382" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Болт M20×45-8,8</t>
+          <t>Болт M10×45-8.8</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -10505,7 +10501,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
@@ -10517,25 +10513,25 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1040004505</t>
+          <t>1040004511</t>
         </is>
       </c>
       <c r="B383" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Болт M24×280-10,9</t>
+          <t>Болт M12×30-8,8; Болт M12×30-8.8; Болт M6×16-A2-70</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>JB/T5782</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
@@ -10547,15 +10543,15 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>1040004508</t>
+          <t>1040004517</t>
         </is>
       </c>
       <c r="B384" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Болт M10×45-8.8</t>
+          <t>Болт; Болт M8×16-8,8</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -10565,7 +10561,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
+          <t>Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Сборка ходового делительного клапана 00773605200800000; Масляный радиатор 00773605205400000</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
@@ -10577,15 +10573,15 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>1040004511</t>
+          <t>1040004518</t>
         </is>
       </c>
       <c r="B385" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Болт M12×30-8,8; Болт M12×30-8.8; Болт M6×16-A2-70</t>
+          <t>Болт M8×20-8,8; Болт</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -10595,7 +10591,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Шасси 00773602800000000; Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
@@ -10607,15 +10603,15 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1040004517</t>
+          <t>1040004519</t>
         </is>
       </c>
       <c r="B386" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Болт; Болт M8×16-8,8</t>
+          <t>Болт M8×25-8,8; Болт</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -10625,7 +10621,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Шасси 00773602800000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Сборка ходового делительного клапана 00773605200800000; Масляный радиатор 00773605205400000</t>
+          <t>Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема топлива 00773607100400000; Сборка клапан ходового управления 00773605201000000</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
@@ -10637,15 +10633,15 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1040004518</t>
+          <t>1040004520</t>
         </is>
       </c>
       <c r="B387" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Болт M8×20-8,8; Болт</t>
+          <t>Болт M8×30-8,8; Болт</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -10655,7 +10651,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Шасси 00773602800000000; Cистема отвода тепла 00773607100600000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -10667,15 +10663,15 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1040004519</t>
+          <t>1040004522</t>
         </is>
       </c>
       <c r="B388" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Болт M8×25-8,8; Болт</t>
+          <t>Болт M8×50-8,8; Болт M8×50; Винт M8×50-8.8</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -10685,7 +10681,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема топлива 00773607100400000; Сборка клапан ходового управления 00773605201000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Башенная стрела в сборе 00773700400000000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -10697,25 +10693,25 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1040004520</t>
+          <t>1040004553</t>
         </is>
       </c>
       <c r="B389" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Болт M8×30-8,8; Болт</t>
+          <t>Болт M6×35-8,8</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5783; GB/5783</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -10727,25 +10723,25 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1040004522</t>
+          <t>1040004556</t>
         </is>
       </c>
       <c r="B390" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Болт M8×50-8,8; Болт M8×50; Винт M8×50-8.8</t>
+          <t>Болт M12×35-8,8</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T16674.1</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Башенная стрела в сборе 00773700400000000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
@@ -10757,25 +10753,25 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>1040004553</t>
+          <t>1040004557</t>
         </is>
       </c>
       <c r="B391" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Болт M6×35-8,8</t>
+          <t>Болт M8×50-8,8</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>JB/T5783; GB/5783</t>
+          <t>JB/T16674.1</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
@@ -10787,25 +10783,25 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>1040004556</t>
+          <t>1040004565</t>
         </is>
       </c>
       <c r="B392" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Болт M12×35-8,8</t>
+          <t>Болт M10×30-8,8-DKL; Болт M16×30-8,8-DKL</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>JB/T16674.1</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
@@ -10817,25 +10813,25 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1040004557</t>
+          <t>1040004570</t>
         </is>
       </c>
       <c r="B393" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Болт M8×50-8,8</t>
+          <t>Болт M16×30-8,8</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>JB/T16674.1</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -10847,15 +10843,15 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>1040004565</t>
+          <t>1040004590</t>
         </is>
       </c>
       <c r="B394" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Болт M10×30-8,8-DKL; Болт M16×30-8,8-DKL</t>
+          <t>Болт M8×14-8,8</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
@@ -10865,7 +10861,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Капот 00773601100000000</t>
+          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
@@ -10877,15 +10873,15 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1040004570</t>
+          <t>1040004591</t>
         </is>
       </c>
       <c r="B395" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Болт M16×30-8,8</t>
+          <t>Болт M3×8-8.8</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -10895,7 +10891,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
@@ -10907,25 +10903,25 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1040004590</t>
+          <t>1040004603</t>
         </is>
       </c>
       <c r="B396" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Болт M8×14-8,8</t>
+          <t>Болт M8×75-8,8</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5782</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
@@ -10937,25 +10933,25 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>1040004591</t>
+          <t>1040004613</t>
         </is>
       </c>
       <c r="B397" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Болт M3×8-8.8</t>
+          <t>Болт M24×60-10,9</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5782</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Балансир 00773601000000000</t>
         </is>
       </c>
       <c r="F397" t="inlineStr">
@@ -10967,25 +10963,25 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>1040004603</t>
+          <t>1040004619</t>
         </is>
       </c>
       <c r="B398" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Болт M8×75-8,8</t>
+          <t>Болт M8×35-8,8; Болт</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>JB/T5782</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Консоль 00773700200000000; Поворотная платформа 00773600800000000; Вытяжная система 00773607101000000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
@@ -10997,25 +10993,25 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>1040004613</t>
+          <t>1040004646</t>
         </is>
       </c>
       <c r="B399" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Болт M24×60-10,9</t>
+          <t>Винт M10×15-8</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>JB/T5782</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Балансир 00773601000000000</t>
+          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
@@ -11027,25 +11023,25 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1040004619</t>
+          <t>1040004648</t>
         </is>
       </c>
       <c r="B400" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Болт M8×35-8,8; Болт</t>
+          <t>Болт M16×90-10,9</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T1228</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Консоль 00773700200000000; Поворотная платформа 00773600800000000; Вытяжная система 00773607101000000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000</t>
+          <t>Поворотный механизм 00773700900000000</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
@@ -11057,25 +11053,25 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>1040004646</t>
+          <t>1040004649</t>
         </is>
       </c>
       <c r="B401" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Винт M10×15-8</t>
+          <t>Винт 5/8-11UNC×45-10.9</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>ANSIB18.3</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
@@ -11087,25 +11083,25 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>1040004648</t>
+          <t>1040004650</t>
         </is>
       </c>
       <c r="B402" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Болт M16×90-10,9</t>
+          <t>Болт 7/16-14UNF×35-10.9</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>JB/T1228</t>
+          <t>ANSIB18.3</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Поворотный механизм 00773700900000000</t>
+          <t>Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
@@ -11117,25 +11113,25 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>1040004649</t>
+          <t>1040004653</t>
         </is>
       </c>
       <c r="B403" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Винт 5/8-11UNC×45-10.9</t>
+          <t>Болт M12×30-10,9</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>ANSIB18.3</t>
+          <t>JB/T15783; JB/T5783</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Гидравлический насос в сборе 00773605200400000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
@@ -11147,25 +11143,25 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1040004650</t>
+          <t>1040004654</t>
         </is>
       </c>
       <c r="B404" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Болт 7/16-14UNF×35-10.9</t>
+          <t>Болт M16×1,5×40-10,9</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>ANSIB18.3</t>
+          <t>JB/T5787</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Сборка ходового мотора 00773605200600000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
@@ -11177,25 +11173,25 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1040004653</t>
+          <t>1040004672</t>
         </is>
       </c>
       <c r="B405" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Болт M12×30-10,9</t>
+          <t>Болт M5×10-8,8; Болт M5×10-8.8</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>JB/T15783; JB/T5783</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F405" t="inlineStr">
@@ -11207,25 +11203,25 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1040004654</t>
+          <t>1040004678</t>
         </is>
       </c>
       <c r="B406" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Болт M16×1,5×40-10,9</t>
+          <t>Болт для ограничителя открывания двери M10×70</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>JB/T5787</t>
+          <t>M10×70</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -11237,25 +11233,25 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>1040004672</t>
+          <t>1040005840</t>
         </is>
       </c>
       <c r="B407" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Болт M5×10-8,8; Болт M5×10-8.8</t>
+          <t>Болт M16×100-10,9</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T1228</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Башенная стрела в сборе 00773700400000000</t>
+          <t>Поворотный механизм 00773700900000000</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -11267,25 +11263,25 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>1040004678</t>
+          <t>1040005844</t>
         </is>
       </c>
       <c r="B408" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Болт для ограничителя открывания двери M10×70</t>
+          <t>Болт M6×10-A2-70; Болт M6×10</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>M10×70</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -11297,25 +11293,25 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1040005840</t>
+          <t>1040005852</t>
         </is>
       </c>
       <c r="B409" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Болт M16×100-10,9</t>
+          <t>Болт M12×20-8,8</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>JB/T1228</t>
+          <t>JB/T5787</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Поворотный механизм 00773700900000000</t>
+          <t>Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -11327,25 +11323,25 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1040005844</t>
+          <t>1040005925</t>
         </is>
       </c>
       <c r="B410" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Болт M6×10-A2-70; Болт M6×10</t>
+          <t>Болт M6×80</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T5782</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -11357,7 +11353,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1040005852</t>
+          <t>1040100069</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -11365,17 +11361,17 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Болт M12×20-8,8</t>
+          <t>Винт M8×20-8.8</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>JB/T5787</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000</t>
+          <t>Фильтр высокого давления в сборе 00773605201800000</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -11387,25 +11383,25 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1040005925</t>
+          <t>1040100087</t>
         </is>
       </c>
       <c r="B412" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Болт M6×80</t>
+          <t>Винт</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>JB/T5782</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -11417,15 +11413,15 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>1040100069</t>
+          <t>1040100097</t>
         </is>
       </c>
       <c r="B413" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Винт M8×20-8.8</t>
+          <t>Винт</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -11435,7 +11431,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Фильтр высокого давления в сборе 00773605201800000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
@@ -11447,15 +11443,15 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1040100087</t>
+          <t>1040100105</t>
         </is>
       </c>
       <c r="B414" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Винт</t>
+          <t>Винт M6×25-8.8</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -11465,7 +11461,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -11477,25 +11473,25 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1040100097</t>
+          <t>1040100148</t>
         </is>
       </c>
       <c r="B415" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Винт</t>
+          <t>Винт M8×45-8.8</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T5783</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -11507,15 +11503,15 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>1040100105</t>
+          <t>1040100438</t>
         </is>
       </c>
       <c r="B416" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Винт M6×25-8.8</t>
+          <t>Винт M5×55-8.8</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
@@ -11525,7 +11521,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Капот 00773601100000000</t>
+          <t>Селекторный клапан платформы в сборе 00773605201200000</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -11537,25 +11533,25 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1040100148</t>
+          <t>1040100714</t>
         </is>
       </c>
       <c r="B417" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Винт M8×45-8.8</t>
+          <t>Винт M12×130-8.8</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>JB/T5783</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -11567,25 +11563,21 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1040100438</t>
+          <t>1040101461</t>
         </is>
       </c>
       <c r="B418" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Винт M5×55-8.8</t>
-        </is>
-      </c>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>JB/T70.1</t>
-        </is>
-      </c>
+          <t>Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Селекторный клапан платформы в сборе 00773605201200000</t>
+          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
@@ -11597,25 +11589,21 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>1040100714</t>
+          <t>1040101464</t>
         </is>
       </c>
       <c r="B419" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Винт M12×130-8.8</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>JB/T70.1</t>
-        </is>
-      </c>
+          <t>Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
@@ -11627,21 +11615,25 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>1040101461</t>
+          <t>1040101492</t>
         </is>
       </c>
       <c r="B420" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
-        </is>
-      </c>
-      <c r="D420" t="inlineStr"/>
+          <t>Винт M10×25; Винт M10×25-8,8</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>JB/T70.1</t>
+        </is>
+      </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -11653,21 +11645,21 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>1040101464</t>
+          <t>1040101628</t>
         </is>
       </c>
       <c r="B421" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Резьбовая заглушка</t>
         </is>
       </c>
       <c r="D421" t="inlineStr"/>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Сборка блока маслоканала 00773605202600000</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -11679,25 +11671,25 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>1040101492</t>
+          <t>1040101692</t>
         </is>
       </c>
       <c r="B422" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Винт M10×25; Винт M10×25-8,8</t>
+          <t>Болт</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T5786</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Гидравлический бак в сборе 00773605200200000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -11709,21 +11701,25 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>1040101628</t>
+          <t>1040101995</t>
         </is>
       </c>
       <c r="B423" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Резьбовая заглушка</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr"/>
+          <t>Винт   M10×30-8.8</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>JB/T70.1</t>
+        </is>
+      </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Сборка блока маслоканала 00773605202600000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -11735,25 +11731,25 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>1040101692</t>
+          <t>1040102037</t>
         </is>
       </c>
       <c r="B424" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Болт</t>
+          <t>Болт M8×70-8,8</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>JB/T5786</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Сборка блока маслоканала 00773605202600000</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -11765,15 +11761,15 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>1040101995</t>
+          <t>1040102372</t>
         </is>
       </c>
       <c r="B425" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Винт   M10×30-8.8</t>
+          <t>Винт с цилиндрической головкой и внутренней шестигранью</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -11783,7 +11779,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -11795,25 +11791,25 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>1040102037</t>
+          <t>1040102646</t>
         </is>
       </c>
       <c r="B426" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Болт M8×70-8,8</t>
+          <t>Винт M6×12-8.8</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T70.3</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Сборка блока маслоканала 00773605202600000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -11825,15 +11821,15 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>1040102372</t>
+          <t>1040102737</t>
         </is>
       </c>
       <c r="B427" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Винт с цилиндрической головкой и внутренней шестигранью</t>
+          <t>Винт M8×30-8,8</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
@@ -11843,7 +11839,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Cистема топлива 00773607100400000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -11855,25 +11851,25 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>1040102646</t>
+          <t>1040102739</t>
         </is>
       </c>
       <c r="B428" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Винт M6×12-8.8</t>
+          <t>Винт M8×60-8.8</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>JB/T70.3</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Сборка клапан ходового управления 00773605201000000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -11885,15 +11881,15 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1040102737</t>
+          <t>1040102741</t>
         </is>
       </c>
       <c r="B429" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Винт M8×30-8,8</t>
+          <t>Винт M10×40-8,8</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -11903,7 +11899,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -11915,15 +11911,15 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1040102739</t>
+          <t>1040102751</t>
         </is>
       </c>
       <c r="B430" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Винт M8×60-8.8</t>
+          <t>Винт   M5×25-8.8</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -11933,7 +11929,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Сборка клапан ходового управления 00773605201000000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -11945,25 +11941,25 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>1040102741</t>
+          <t>1040102757</t>
         </is>
       </c>
       <c r="B431" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Винт M10×40-8,8</t>
+          <t>Винт M10×25-8,8</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T70.3</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Балансир 00773601000000000</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -11975,15 +11971,15 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>1040102751</t>
+          <t>1040102761</t>
         </is>
       </c>
       <c r="B432" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Винт   M5×25-8.8</t>
+          <t>Винт   M10×20-8.8</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -11993,7 +11989,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -12005,25 +12001,25 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>1040102757</t>
+          <t>1040102773</t>
         </is>
       </c>
       <c r="B433" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Винт M10×25-8,8</t>
+          <t>Винт M6×40-8.8</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>JB/T70.3</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Балансир 00773601000000000</t>
+          <t>Рабочая платформа 00773700100000000</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -12035,15 +12031,15 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>1040102761</t>
+          <t>1040102774</t>
         </is>
       </c>
       <c r="B434" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Винт   M10×20-8.8</t>
+          <t>Винт M6×15-8.8</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -12053,7 +12049,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Сборка селекторного клапана выравнивания 00773605202200000</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -12065,15 +12061,15 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>1040102773</t>
+          <t>1040102778</t>
         </is>
       </c>
       <c r="B435" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Винт M6×40-8.8</t>
+          <t>Винт M6×10-8.8; Винт M6×10</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -12083,7 +12079,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -12095,25 +12091,25 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>1040102774</t>
+          <t>1040103076</t>
         </is>
       </c>
       <c r="B436" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Винт M6×15-8.8</t>
+          <t>Винт M8×16-8.8; Винт M10×16-8,8; Винт M8×16-8,8</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T70.3</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Сборка селекторного клапана выравнивания 00773605202200000</t>
+          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Буксирная система 00773700700000000; Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -12125,15 +12121,15 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1040102778</t>
+          <t>1040103111</t>
         </is>
       </c>
       <c r="B437" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Винт M6×10-8.8; Винт M6×10</t>
+          <t>Винт M8×16-8.8</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -12143,7 +12139,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000</t>
+          <t>Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -12155,25 +12151,25 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1040103076</t>
+          <t>1040103114</t>
         </is>
       </c>
       <c r="B438" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Винт M8×16-8.8; Винт M10×16-8,8; Винт M8×16-8,8</t>
+          <t>Винт M8×45-8.8</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>JB/T70.3</t>
+          <t>JB/T70.1</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Буксирная система 00773700700000000; Башенная стрела в сборе 00773700400000000</t>
+          <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -12185,15 +12181,15 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>1040103111</t>
+          <t>1040103118</t>
         </is>
       </c>
       <c r="B439" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Винт M8×16-8.8</t>
+          <t>Винт M8×100-8.8</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -12203,7 +12199,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -12215,25 +12211,25 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>1040103114</t>
+          <t>1040103133</t>
         </is>
       </c>
       <c r="B440" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Винт M8×45-8.8</t>
+          <t>Винт M5×30; Винт M6×30-A2-70</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T70.3</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
+          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -12245,25 +12241,25 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>1040103118</t>
+          <t>1040103164</t>
         </is>
       </c>
       <c r="B441" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Винт M8×100-8.8</t>
+          <t>Винт   M10×30-8.8</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>JB/T70.1</t>
+          <t>JB/T70.3</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -12275,25 +12271,21 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1040103133</t>
+          <t>1040114040</t>
         </is>
       </c>
       <c r="B442" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>Винт M5×30; Винт M6×30-A2-70</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>JB/T70.3</t>
-        </is>
-      </c>
+          <t>Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000</t>
+          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -12305,25 +12297,21 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1040103164</t>
+          <t>1040114701</t>
         </is>
       </c>
       <c r="B443" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Винт   M10×30-8.8</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>JB/T70.3</t>
-        </is>
-      </c>
+          <t>Прямой удлиненный соединитель</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -12335,21 +12323,25 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>1040114040</t>
+          <t>1040200113</t>
         </is>
       </c>
       <c r="B444" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr"/>
+          <t>Гайка M10-8</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>JB/T6170</t>
+        </is>
+      </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
+          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -12361,21 +12353,25 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>1040114701</t>
+          <t>1040200161</t>
         </is>
       </c>
       <c r="B445" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Прямой удлиненный соединитель</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr"/>
+          <t>Гайка</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>JB/T889</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -12387,25 +12383,25 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>1040200113</t>
+          <t>1040200170</t>
         </is>
       </c>
       <c r="B446" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Гайка M10-8</t>
+          <t>Гайка</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>JB/T6170</t>
+          <t>JB/T889</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
+          <t>Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -12417,11 +12413,11 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1040200161</t>
+          <t>1040200304</t>
         </is>
       </c>
       <c r="B447" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C447" t="inlineStr">
         <is>
@@ -12435,7 +12431,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Двигатель 00773607100200000</t>
+          <t>Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -12447,11 +12443,11 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1040200170</t>
+          <t>1040200398</t>
         </is>
       </c>
       <c r="B448" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C448" t="inlineStr">
         <is>
@@ -12460,12 +12456,12 @@
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>JB/T889</t>
+          <t>JB/T6177.1</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Cистема отвода тепла 00773607100600000</t>
+          <t>Вытяжная система 00773607101000000</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -12477,25 +12473,25 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>1040200304</t>
+          <t>1040200503</t>
         </is>
       </c>
       <c r="B449" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Гайка</t>
+          <t>Гайка M8-8; Гайка</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>JB/T889</t>
+          <t>JB/T889.1</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Cистема топлива 00773607100400000</t>
+          <t>Рабочая платформа 00773700110000000; Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Шасси 00773602800000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000; Сборка клапан ходового управления 00773605201000000; Сборка блока маслоканала 00773605202600000</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -12507,25 +12503,25 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>1040200398</t>
+          <t>1040200504</t>
         </is>
       </c>
       <c r="B450" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Гайка</t>
+          <t>Гайка M10-8</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>JB/T6177.1</t>
+          <t>JB/T889.1</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Вытяжная система 00773607101000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -12537,15 +12533,15 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1040200503</t>
+          <t>1040200507</t>
         </is>
       </c>
       <c r="B451" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Гайка M8-8; Гайка</t>
+          <t>Гайка</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -12555,7 +12551,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700110000000; Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Шасси 00773602800000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000; Сборка клапан ходового управления 00773605201000000; Сборка блока маслоканала 00773605202600000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -12567,25 +12563,25 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1040200504</t>
+          <t>1040201089</t>
         </is>
       </c>
       <c r="B452" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Гайка M10-8</t>
+          <t>Гайка M8-8</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>JB/T889.1</t>
+          <t>JB/T6170</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -12597,25 +12593,25 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1040200507</t>
+          <t>1040201111</t>
         </is>
       </c>
       <c r="B453" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Гайка</t>
+          <t>Гайка M24 -10</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>JB/T889.1</t>
+          <t>JB/T889</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -12627,15 +12623,15 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>1040201089</t>
+          <t>1040201381</t>
         </is>
       </c>
       <c r="B454" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Гайка M8-8</t>
+          <t>Гайка M12-8</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -12645,7 +12641,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Поворотная платформа 00773600800000000; Капот 00773601100000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
@@ -12657,7 +12653,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>1040201111</t>
+          <t>1040201743</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -12665,17 +12661,17 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Гайка M24 -10</t>
+          <t>Гайка M6</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>JB/T889</t>
+          <t>QC/T608</t>
         </is>
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
@@ -12687,7 +12683,7 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1040201381</t>
+          <t>1040201880</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -12695,17 +12691,17 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Гайка M12-8</t>
+          <t>Гайка M8-6</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>JB/T6170</t>
+          <t>JB/T802</t>
         </is>
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
@@ -12717,25 +12713,25 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1040201743</t>
+          <t>1040201896</t>
         </is>
       </c>
       <c r="B457" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Гайка M6</t>
+          <t>Гайка M6-8; Гайка</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>QC/T608</t>
+          <t>JB/T889.1</t>
         </is>
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F457" t="inlineStr">
@@ -12747,15 +12743,15 @@
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1040201880</t>
+          <t>1040201902</t>
         </is>
       </c>
       <c r="B458" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Гайка M8-6</t>
+          <t>Гайка M6-6; Гайка M6-8</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
@@ -12777,15 +12773,15 @@
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1040201896</t>
+          <t>1040201904</t>
         </is>
       </c>
       <c r="B459" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Гайка M6-8; Гайка</t>
+          <t>Гайка M5-8</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
@@ -12795,7 +12791,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Cистема топлива 00773607100400000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
@@ -12807,25 +12803,25 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1040201902</t>
+          <t>1040202297</t>
         </is>
       </c>
       <c r="B460" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Гайка M6-6; Гайка M6-8</t>
+          <t>Гайка M16×1,5-10(Spiralock)</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>JB/T802</t>
+          <t>JB/T6177.2</t>
         </is>
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
@@ -12837,25 +12833,25 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1040201904</t>
+          <t>1040300060</t>
         </is>
       </c>
       <c r="B461" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Гайка M5-8</t>
+          <t>Шайба 5</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>JB/T889.1</t>
+          <t>JB/T93</t>
         </is>
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Селекторный клапан платформы в сборе 00773605201200000</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
@@ -12867,25 +12863,25 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1040202297</t>
+          <t>1040300186</t>
         </is>
       </c>
       <c r="B462" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Гайка M16×1,5-10(Spiralock)</t>
+          <t>Шайба</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>JB/T6177.2</t>
+          <t>JB/T1230</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Поворотный механизм 00773700900000000</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
@@ -12897,25 +12893,25 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>1040300060</t>
+          <t>1040300514</t>
         </is>
       </c>
       <c r="B463" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Шайба 5</t>
+          <t>Шайба 5-200HV</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>JB/T93</t>
+          <t>JB/T97.1</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Селекторный клапан платформы в сборе 00773605201200000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
@@ -12927,25 +12923,25 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>1040300186</t>
+          <t>1040300735</t>
         </is>
       </c>
       <c r="B464" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Шайба</t>
+          <t>Шайба 6-200HV</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>JB/T1230</t>
+          <t>JB/T96.1</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Поворотный механизм 00773700900000000</t>
+          <t>Рабочая платформа 00773700100000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
@@ -12957,25 +12953,25 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>1040300514</t>
+          <t>1040300771</t>
         </is>
       </c>
       <c r="B465" t="n">
-        <v>32</v>
+        <v>171</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Шайба 5-200HV</t>
+          <t>Шайба 6-200HV; Шайба GB/T97.1 -2002; Шайба; Шайба 6</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>JB/T97.1</t>
+          <t>JB/T97.1; 6-200HV</t>
         </is>
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Буксирная система 00773700700000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Cистема топлива 00773607100400000; Главный клапан в сборе 00773605201600000; Сборка селекторного клапана выравнивания 00773605202200000</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
@@ -12987,15 +12983,15 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>1040300735</t>
+          <t>1040301031</t>
         </is>
       </c>
       <c r="B466" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Шайба 6-200HV</t>
+          <t>Шайба 12-300HV; Прокладка 12-200HV</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -13005,7 +13001,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
@@ -13017,25 +13013,25 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1040300771</t>
+          <t>1040301502</t>
         </is>
       </c>
       <c r="B467" t="n">
-        <v>171</v>
+        <v>6</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Шайба 6-200HV; Шайба GB/T97.1 -2002; Шайба; Шайба 6</t>
+          <t>Шайба 10</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>JB/T97.1; 6-200HV</t>
+          <t>JB/T93</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Cистема топлива 00773607100400000; Главный клапан в сборе 00773605201600000; Сборка селекторного клапана выравнивания 00773605202200000</t>
+          <t>Капот 00773601100000000; Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
@@ -13047,7 +13043,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1040301031</t>
+          <t>1040301503</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -13055,17 +13051,17 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Шайба 12-300HV; Прокладка 12-200HV</t>
+          <t>Шайба 12</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>JB/T96.1</t>
+          <t>JB/T93</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
@@ -13077,15 +13073,15 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>1040301502</t>
+          <t>1040301510</t>
         </is>
       </c>
       <c r="B469" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Шайба 10</t>
+          <t>Шайба 8</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -13095,7 +13091,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000; Гидравлический бак в сборе 00773605200200000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Капот 00773601100000000; Шасси 00773602800000000; Гидравлический бак в сборе 00773605200200000; Фильтр высокого давления в сборе 00773605201800000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000; Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
@@ -13107,25 +13103,25 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>1040301503</t>
+          <t>1040301511</t>
         </is>
       </c>
       <c r="B470" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Шайба 12</t>
+          <t>Шайба 24-200HV</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>JB/T93</t>
+          <t>JB/T97.1</t>
         </is>
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F470" t="inlineStr">
@@ -13137,25 +13133,25 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>1040301510</t>
+          <t>1040301515</t>
         </is>
       </c>
       <c r="B471" t="n">
-        <v>91</v>
+        <v>218</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Шайба 8</t>
+          <t>Шайба 8-200HV; Шайба 8; Шайба</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>JB/T93</t>
+          <t>JB/T97.1; 8-200HV</t>
         </is>
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Капот 00773601100000000; Шасси 00773602800000000; Гидравлический бак в сборе 00773605200200000; Фильтр высокого давления в сборе 00773605201800000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000; Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000; Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Буксирная система 00773700700000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Шасси 00773602800000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000; Фильтр высокого давления в сборе 00773605201800000; Масляный радиатор 00773605205400000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F471" t="inlineStr">
@@ -13167,15 +13163,15 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>1040301511</t>
+          <t>1040302410</t>
         </is>
       </c>
       <c r="B472" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Шайба 24-200HV</t>
+          <t>Шайба 4-200HV</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -13185,7 +13181,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Поворотная платформа 00773600800000000</t>
         </is>
       </c>
       <c r="F472" t="inlineStr">
@@ -13197,25 +13193,25 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>1040301515</t>
+          <t>1040302480</t>
         </is>
       </c>
       <c r="B473" t="n">
-        <v>218</v>
+        <v>96</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Шайба 8-200HV; Шайба 8; Шайба</t>
+          <t>Шайба 8-200HV; Шайба</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>JB/T97.1; 8-200HV</t>
+          <t>JB/T96.1</t>
         </is>
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Консоль 00773700200000000; Верхняя стрела в сборе 00773600300000000; Буксирная система 00773700700000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Шасси 00773602800000000; Вытяжная система 00773607101000000; Впускная система 00773607100800000; Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000; Фильтр высокого давления в сборе 00773605201800000; Масляный радиатор 00773605205400000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Рабочая платформа 00773700110000000; Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Впускная система 00773607100800000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F473" t="inlineStr">
@@ -13227,25 +13223,25 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>1040302410</t>
+          <t>1040302483</t>
         </is>
       </c>
       <c r="B474" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Шайба 4-200HV</t>
+          <t>Шайба 24-200HV</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>JB/T97.1</t>
+          <t>JB/T96.1</t>
         </is>
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000</t>
+          <t>Балансир 00773601000000000</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
@@ -13257,25 +13253,25 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>1040302480</t>
+          <t>1040302489</t>
         </is>
       </c>
       <c r="B475" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Шайба 8-200HV; Шайба</t>
+          <t>Шайба 10-200HV; Прокладка 10-200HV; Шайба; Шайба 10</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>JB/T96.1</t>
+          <t>JB/T97.1</t>
         </is>
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700110000000; Буксирная система 00773700700000000; Поворотная платформа 00773600800000000; Капот 00773601100000000; Впускная система 00773607100800000; Cистема топлива 00773607100400000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Двигатель 00773607100200000; Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
@@ -13287,25 +13283,25 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1040302483</t>
+          <t>1040302490</t>
         </is>
       </c>
       <c r="B476" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Шайба 24-200HV</t>
+          <t>Шайба 12-200HV; Шайба 12; Шайба</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>JB/T96.1</t>
+          <t>JB/T97.1; JB/T70.1</t>
         </is>
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Балансир 00773601000000000</t>
+          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Двигатель 00773607100200000; Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
@@ -13317,15 +13313,15 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1040302489</t>
+          <t>1040302492</t>
         </is>
       </c>
       <c r="B477" t="n">
-        <v>73</v>
+        <v>28</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Шайба 10-200HV; Прокладка 10-200HV; Шайба; Шайба 10</t>
+          <t>Шайба 16-200HV; Шайба</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -13335,7 +13331,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000; Верхняя стрела в сборе 00773600300000000; Поворотная платформа 00773600800000000; Двигатель 00773607100200000; Сборка аварийного насоса с приводом от электродвигателя 00773605202000000</t>
+          <t>Шасси 00773602800000000; Двигатель 00773607100200000</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
@@ -13347,25 +13343,25 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1040302490</t>
+          <t>1040302493</t>
         </is>
       </c>
       <c r="B478" t="n">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Шайба 12-200HV; Шайба 12; Шайба</t>
+          <t>Шайба 20-200HV</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>JB/T97.1; JB/T70.1</t>
+          <t>JB/T97.1</t>
         </is>
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Верхняя стрела в сборе 00773600300000000; Башенная стрела в сборе 00773700400000000; Поворотная платформа 00773600800000000; Двигатель 00773607100200000; Сборка ходового мотора 00773605200600000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
@@ -13377,25 +13373,25 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>1040302492</t>
+          <t>1040302512</t>
         </is>
       </c>
       <c r="B479" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Шайба 16-200HV; Шайба</t>
+          <t>Шайба 10-200HV; Шайба</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>JB/T97.1</t>
+          <t>JB/T96.1</t>
         </is>
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000; Двигатель 00773607100200000</t>
+          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
@@ -13407,7 +13403,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>1040302493</t>
+          <t>1040302513</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -13415,17 +13411,17 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Шайба 20-200HV</t>
+          <t>Шайба 16-200HV</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>JB/T97.1</t>
+          <t>JB/T96.1</t>
         </is>
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Шасси 00773602800000000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
@@ -13437,15 +13433,15 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>1040302512</t>
+          <t>1040302529</t>
         </is>
       </c>
       <c r="B481" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Шайба 10-200HV; Шайба</t>
+          <t>Шайба 5</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -13455,7 +13451,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000; Капот 00773601100000000; Cистема топлива 00773607100400000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
@@ -13467,15 +13463,15 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1040302513</t>
+          <t>1040302821</t>
         </is>
       </c>
       <c r="B482" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Шайба 16-200HV</t>
+          <t>Шайба 12-200HV; Шайба; Шайба 12</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -13485,7 +13481,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Поворотная платформа 00773600800000000; Cистема отвода тепла 00773607100600000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
@@ -13497,25 +13493,21 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>1040302529</t>
+          <t>1081000673</t>
         </is>
       </c>
       <c r="B483" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Шайба 5</t>
-        </is>
-      </c>
-      <c r="D483" t="inlineStr">
-        <is>
-          <t>JB/T96.1</t>
-        </is>
-      </c>
+          <t>Сложная уплотнительная шайба</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
@@ -13527,25 +13519,21 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1040302821</t>
+          <t>1089900652</t>
         </is>
       </c>
       <c r="B484" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Шайба 12-200HV; Шайба; Шайба 12</t>
-        </is>
-      </c>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>JB/T96.1</t>
-        </is>
-      </c>
+          <t>Уплотнительная полоса</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Поворотная платформа 00773600800000000; Cистема отвода тепла 00773607100600000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
@@ -13557,21 +13545,25 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>1081000673</t>
+          <t>1100700163</t>
         </is>
       </c>
       <c r="B485" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Сложная уплотнительная шайба</t>
-        </is>
-      </c>
-      <c r="D485" t="inlineStr"/>
+          <t>Дверная ручка</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>26983-09</t>
+        </is>
+      </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Cистема топлива 00773607100400000</t>
+          <t>Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
@@ -13583,21 +13575,21 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1089900652</t>
+          <t>1101000166</t>
         </is>
       </c>
       <c r="B486" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Уплотнительная полоса</t>
+          <t>Петля ZJ14600Z</t>
         </is>
       </c>
       <c r="D486" t="inlineStr"/>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
@@ -13609,20 +13601,20 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>1100700163</t>
+          <t>1109900765</t>
         </is>
       </c>
       <c r="B487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Дверная ручка</t>
+          <t>Гидравлический дверной замок</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>26983-09</t>
+          <t>50075-C37K</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
@@ -13639,15 +13631,15 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1101000166</t>
+          <t>1109900766</t>
         </is>
       </c>
       <c r="B488" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Петля ZJ14600Z</t>
+          <t>Дверной замок аккумулятора</t>
         </is>
       </c>
       <c r="D488" t="inlineStr"/>
@@ -13665,25 +13657,21 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1109900765</t>
+          <t>1109900921</t>
         </is>
       </c>
       <c r="B489" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Гидравлический дверной замок</t>
-        </is>
-      </c>
-      <c r="D489" t="inlineStr">
-        <is>
-          <t>50075-C37K</t>
-        </is>
-      </c>
+          <t>Пластичная пробка M36</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000</t>
+          <t>Балансир 00773601000000000</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
@@ -13695,7 +13683,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>1109900766</t>
+          <t>1109900986</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -13703,13 +13691,13 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Дверной замок аккумулятора</t>
+          <t>Соединитель  буксируемой  цепи I E4.421.12.1.1</t>
         </is>
       </c>
       <c r="D490" t="inlineStr"/>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
@@ -13721,21 +13709,21 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1109900921</t>
+          <t>1109900987</t>
         </is>
       </c>
       <c r="B491" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Пластичная пробка M36</t>
+          <t>Соединитель  буксируемой  цепи II E4.421.12.1.2</t>
         </is>
       </c>
       <c r="D491" t="inlineStr"/>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Балансир 00773601000000000</t>
+          <t>Буксирная система 00773700700000000</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
@@ -13747,15 +13735,15 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>1109900986</t>
+          <t>1109900988</t>
         </is>
       </c>
       <c r="B492" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Соединитель  буксируемой  цепи I E4.421.12.1.1</t>
+          <t>Внешняя боковая пластина цепи E4.42.01</t>
         </is>
       </c>
       <c r="D492" t="inlineStr"/>
@@ -13773,15 +13761,15 @@
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>1109900987</t>
+          <t>1109900990</t>
         </is>
       </c>
       <c r="B493" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Соединитель  буксируемой  цепи II E4.421.12.1.2</t>
+          <t>Внутренняя боковая пластина цепи E4.42.02.075.0</t>
         </is>
       </c>
       <c r="D493" t="inlineStr"/>
@@ -13799,15 +13787,15 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1109900988</t>
+          <t>1109900991</t>
         </is>
       </c>
       <c r="B494" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Внешняя боковая пластина цепи E4.42.01</t>
+          <t>Горизонтальная перегородка буксируемой цепи 385.12</t>
         </is>
       </c>
       <c r="D494" t="inlineStr"/>
@@ -13825,7 +13813,7 @@
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>1109900990</t>
+          <t>1109900993</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -13833,7 +13821,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Внутренняя боковая пластина цепи E4.42.02.075.0</t>
+          <t>Вертикальная перегородка буксируемой цепи 42.1</t>
         </is>
       </c>
       <c r="D495" t="inlineStr"/>
@@ -13851,21 +13839,25 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1109900991</t>
+          <t>1110100359</t>
         </is>
       </c>
       <c r="B496" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Горизонтальная перегородка буксируемой цепи 385.12</t>
-        </is>
-      </c>
-      <c r="D496" t="inlineStr"/>
+          <t>Удлинение пневматической пружины 435mm,S=162mm,F=900N,M8×20</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>000816</t>
+        </is>
+      </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Капот 00773601100000000</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
@@ -13877,21 +13869,21 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1109900993</t>
+          <t>1140101461</t>
         </is>
       </c>
       <c r="B497" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Вертикальная перегородка буксируемой цепи 42.1</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D497" t="inlineStr"/>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Буксирная система 00773700700000000</t>
+          <t>Сборка ходового делительного клапана 00773605200800000; Сборка клапан ходового управления 00773605201000000; Селекторный клапан платформы в сборе 00773605201200000; Сборка селекторного клапана выравнивания 00773605202200000</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
@@ -13903,7 +13895,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>1110100359</t>
+          <t>1140101462</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -13911,17 +13903,13 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Удлинение пневматической пружины 435mm,S=162mm,F=900N,M8×20</t>
-        </is>
-      </c>
-      <c r="D498" t="inlineStr">
-        <is>
-          <t>000816</t>
-        </is>
-      </c>
+          <t>Прямой соединитель; Прямоугольное композитное колено</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Капот 00773601100000000</t>
+          <t>Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
@@ -13933,11 +13921,11 @@
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1140101461</t>
+          <t>1140101463</t>
         </is>
       </c>
       <c r="B499" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C499" t="inlineStr">
         <is>
@@ -13947,7 +13935,7 @@
       <c r="D499" t="inlineStr"/>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Сборка ходового делительного клапана 00773605200800000; Сборка клапан ходового управления 00773605201000000; Селекторный клапан платформы в сборе 00773605201200000; Сборка селекторного клапана выравнивания 00773605202200000</t>
+          <t>Сборка блока маслоканала 00773605202600000</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
@@ -13959,21 +13947,21 @@
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1140101462</t>
+          <t>1140101464</t>
         </is>
       </c>
       <c r="B500" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Прямой соединитель; Прямоугольное композитное колено</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D500" t="inlineStr"/>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра основной стрелы в сборе 00773605203400000; Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Сборка ходового делительного клапана 00773605200800000; Главный клапан в сборе 00773605201600000; Фильтр высокого давления в сборе 00773605201800000; Масляный радиатор 00773605205400000</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
@@ -13985,21 +13973,25 @@
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>1140101463</t>
+          <t>1140101475</t>
         </is>
       </c>
       <c r="B501" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
-        </is>
-      </c>
-      <c r="D501" t="inlineStr"/>
+          <t>Прямоугольное композитное колено</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Только распространяется на решение с использованием взрывозащищенног о клапана</t>
+        </is>
+      </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Сборка блока маслоканала 00773605202600000</t>
+          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
@@ -14011,21 +14003,21 @@
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>1140101464</t>
+          <t>1140101476</t>
         </is>
       </c>
       <c r="B502" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Колено</t>
         </is>
       </c>
       <c r="D502" t="inlineStr"/>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Сборка ходового делительного клапана 00773605200800000; Главный клапан в сборе 00773605201600000; Фильтр высокого давления в сборе 00773605201800000; Масляный радиатор 00773605205400000</t>
+          <t>Сборка селекторного клапана выравнивания 00773605202200000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Центрально-вращающееся соединение в сборе 00773605205200000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
@@ -14037,7 +14029,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1140101475</t>
+          <t>1140101477</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -14045,14 +14037,10 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Прямоугольное композитное колено</t>
-        </is>
-      </c>
-      <c r="D503" t="inlineStr">
-        <is>
-          <t>Только распространяется на решение с использованием взрывозащищенног о клапана</t>
-        </is>
-      </c>
+          <t>Прямоугольное композитное колено; Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
       <c r="E503" t="inlineStr">
         <is>
           <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
@@ -14067,21 +14055,21 @@
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1140101476</t>
+          <t>1140101483</t>
         </is>
       </c>
       <c r="B504" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Колено</t>
+          <t>Тройной композитный штуцер</t>
         </is>
       </c>
       <c r="D504" t="inlineStr"/>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Сборка селекторного клапана выравнивания 00773605202200000; Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Центрально-вращающееся соединение в сборе 00773605205200000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
@@ -14093,21 +14081,21 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1140101477</t>
+          <t>1140101489</t>
         </is>
       </c>
       <c r="B505" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Прямоугольное композитное колено; Прямой соединитель</t>
+          <t>Тройник</t>
         </is>
       </c>
       <c r="D505" t="inlineStr"/>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Масляный радиатор 00773605205400000</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
@@ -14119,21 +14107,21 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>1140101483</t>
+          <t>1140101523</t>
         </is>
       </c>
       <c r="B506" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Тройной композитный штуцер</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D506" t="inlineStr"/>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Сборка ходового делительного клапана 00773605200800000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
@@ -14145,21 +14133,21 @@
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1140101489</t>
+          <t>1140101628</t>
         </is>
       </c>
       <c r="B507" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Тройник</t>
+          <t>Заглушка</t>
         </is>
       </c>
       <c r="D507" t="inlineStr"/>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Масляный радиатор 00773605205400000</t>
+          <t>Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
@@ -14171,21 +14159,21 @@
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1140101523</t>
+          <t>1140101629</t>
         </is>
       </c>
       <c r="B508" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Резьбовая заглушка</t>
         </is>
       </c>
       <c r="D508" t="inlineStr"/>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Сборка ходового делительного клапана 00773605200800000; Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Главный клапан в сборе 00773605201600000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
@@ -14197,7 +14185,7 @@
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1140101628</t>
+          <t>1140101793</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -14205,13 +14193,13 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Заглушка</t>
+          <t>Тройник</t>
         </is>
       </c>
       <c r="D509" t="inlineStr"/>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000</t>
+          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -14223,7 +14211,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1140101629</t>
+          <t>1140101820</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -14231,13 +14219,13 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Резьбовая заглушка</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D510" t="inlineStr"/>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Главный клапан в сборе 00773605201600000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Гидравлический бак в сборе 00773605200200000; Сборка ходового делительного клапана 00773605200800000; Сборка блока маслоканала 00773605202600000</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
@@ -14249,21 +14237,21 @@
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1140101793</t>
+          <t>1140103362</t>
         </is>
       </c>
       <c r="B511" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Тройник</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D511" t="inlineStr"/>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
+          <t>Гидравлический бак в сборе 00773605200200000; Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
@@ -14275,21 +14263,21 @@
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1140101820</t>
+          <t>1140108904</t>
         </is>
       </c>
       <c r="B512" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Колено</t>
         </is>
       </c>
       <c r="D512" t="inlineStr"/>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000; Сборка ходового делительного клапана 00773605200800000; Сборка блока маслоканала 00773605202600000</t>
+          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
@@ -14301,11 +14289,11 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>1140103362</t>
+          <t>1140112820</t>
         </is>
       </c>
       <c r="B513" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
@@ -14315,7 +14303,7 @@
       <c r="D513" t="inlineStr"/>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000; Гидравлический насос в сборе 00773605200400000</t>
+          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
@@ -14327,21 +14315,21 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>1140108904</t>
+          <t>1140112827</t>
         </is>
       </c>
       <c r="B514" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Колено</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D514" t="inlineStr"/>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Центрально-вращающееся соединение в сборе 00773605205200000</t>
+          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
@@ -14353,11 +14341,11 @@
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1140112820</t>
+          <t>1140113353</t>
         </is>
       </c>
       <c r="B515" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
@@ -14367,7 +14355,7 @@
       <c r="D515" t="inlineStr"/>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
+          <t>Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
@@ -14379,11 +14367,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>1140112827</t>
+          <t>1140113717</t>
         </is>
       </c>
       <c r="B516" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
@@ -14393,7 +14381,7 @@
       <c r="D516" t="inlineStr"/>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
+          <t>Гидравлический бак в сборе 00773605200200000</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
@@ -14405,11 +14393,11 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1140113353</t>
+          <t>1140113942</t>
         </is>
       </c>
       <c r="B517" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
@@ -14419,7 +14407,7 @@
       <c r="D517" t="inlineStr"/>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Сборка ходового мотора 00773605200600000</t>
+          <t>Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
@@ -14431,11 +14419,11 @@
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1140113717</t>
+          <t>1140114040</t>
         </is>
       </c>
       <c r="B518" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
@@ -14445,7 +14433,7 @@
       <c r="D518" t="inlineStr"/>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000</t>
+          <t>Гидравлический бак в сборе 00773605200200000; Сборка клапан ходового управления 00773605201000000; Главный клапан в сборе 00773605201600000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
@@ -14457,11 +14445,11 @@
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1140113942</t>
+          <t>1140114045</t>
         </is>
       </c>
       <c r="B519" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
@@ -14483,21 +14471,21 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>1140114040</t>
+          <t>1140114046</t>
         </is>
       </c>
       <c r="B520" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Тройник</t>
         </is>
       </c>
       <c r="D520" t="inlineStr"/>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Гидравлический бак в сборе 00773605200200000; Сборка клапан ходового управления 00773605201000000; Главный клапан в сборе 00773605201600000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
@@ -14509,21 +14497,21 @@
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>1140114045</t>
+          <t>1140114187</t>
         </is>
       </c>
       <c r="B521" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Манометрический штуцер</t>
         </is>
       </c>
       <c r="D521" t="inlineStr"/>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000</t>
+          <t>Сборка клапан ходового управления 00773605201000000; Главный клапан в сборе 00773605201600000</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
@@ -14535,21 +14523,21 @@
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1140114046</t>
+          <t>1140114451</t>
         </is>
       </c>
       <c r="B522" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Тройник</t>
+          <t>Колено</t>
         </is>
       </c>
       <c r="D522" t="inlineStr"/>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000; Отдельный балансировочный клапан в сборе 00773605205600000</t>
+          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
@@ -14561,21 +14549,25 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>1140114187</t>
+          <t>1140114622</t>
         </is>
       </c>
       <c r="B523" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Манометрический штуцер</t>
-        </is>
-      </c>
-      <c r="D523" t="inlineStr"/>
+          <t>Штуцер  колена,  регулируемый по направлению</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Интерфейс Х1 для мотора</t>
+        </is>
+      </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Сборка клапан ходового управления 00773605201000000; Главный клапан в сборе 00773605201600000</t>
+          <t>Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
@@ -14587,21 +14579,21 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>1140114451</t>
+          <t>1140114623</t>
         </is>
       </c>
       <c r="B524" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Колено</t>
+          <t>Прямой соединитель</t>
         </is>
       </c>
       <c r="D524" t="inlineStr"/>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Гидравлическая блокировка нижнего гидроцилиндра выравнивания в сборе 00773605202800000</t>
+          <t>Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
@@ -14613,25 +14605,21 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>1140114622</t>
+          <t>1140114700</t>
         </is>
       </c>
       <c r="B525" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Штуцер  колена,  регулируемый по направлению</t>
-        </is>
-      </c>
-      <c r="D525" t="inlineStr">
-        <is>
-          <t>Интерфейс Х1 для мотора</t>
-        </is>
-      </c>
+          <t>Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Сборка ходового мотора 00773605200600000</t>
+          <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
@@ -14643,7 +14631,7 @@
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>1140114623</t>
+          <t>1140114839</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -14651,13 +14639,13 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Шарнирное соединение; Шарнирное соединение высокого давления</t>
         </is>
       </c>
       <c r="D526" t="inlineStr"/>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Сборка ходового мотора 00773605200600000</t>
+          <t>Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
@@ -14669,7 +14657,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1140114700</t>
+          <t>1140207362</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -14683,7 +14671,7 @@
       <c r="D527" t="inlineStr"/>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Балансировочный клапан верхнего гидроцилиндра выравнивания в сборе 00773605203000000</t>
+          <t>Сборка фильтра низкого давления 00773605201400000</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
@@ -14695,21 +14683,25 @@
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1140114839</t>
+          <t>1149900295</t>
         </is>
       </c>
       <c r="B528" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Шарнирное соединение; Шарнирное соединение высокого давления</t>
-        </is>
-      </c>
-      <c r="D528" t="inlineStr"/>
+          <t>Тройной композитный штуцер</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Только распространяется на решение с использованием взрывозащищенног о клапана</t>
+        </is>
+      </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра консоли в сборе 00773605203200000; Балансировочный клапан гидроцилиндра выдвижения-втягивания в сборе 00773605203800000</t>
+          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
@@ -14721,11 +14713,11 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1140207362</t>
+          <t>1149901685</t>
         </is>
       </c>
       <c r="B529" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
@@ -14735,7 +14727,7 @@
       <c r="D529" t="inlineStr"/>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Сборка фильтра низкого давления 00773605201400000</t>
+          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
@@ -14747,7 +14739,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1149900295</t>
+          <t>1149901793</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -14755,17 +14747,13 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Тройной композитный штуцер</t>
-        </is>
-      </c>
-      <c r="D530" t="inlineStr">
-        <is>
-          <t>Только распространяется на решение с использованием взрывозащищенног о клапана</t>
-        </is>
-      </c>
+          <t>Прямой соединитель</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
@@ -14777,11 +14765,11 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1149901685</t>
+          <t>1149901794</t>
         </is>
       </c>
       <c r="B531" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
@@ -14791,7 +14779,7 @@
       <c r="D531" t="inlineStr"/>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Балансировочный клапан гидроцилиндра башенной стрелы в сборе 00773605203600000</t>
+          <t>Гидравлический насос в сборе 00773605200400000</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
@@ -14803,11 +14791,11 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1149901793</t>
+          <t>1149901795</t>
         </is>
       </c>
       <c r="B532" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
@@ -14817,7 +14805,7 @@
       <c r="D532" t="inlineStr"/>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000</t>
+          <t>Сборка ходового мотора 00773605200600000</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
@@ -14829,21 +14817,21 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>1149901794</t>
+          <t>1159901036</t>
         </is>
       </c>
       <c r="B533" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Пружинная петля</t>
         </is>
       </c>
       <c r="D533" t="inlineStr"/>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Гидравлический насос в сборе 00773605200400000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
@@ -14855,21 +14843,21 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>1149901795</t>
+          <t>1990200692</t>
         </is>
       </c>
       <c r="B534" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Прямой соединитель</t>
+          <t>Резиновая  лента  с  пластическим покрытием</t>
         </is>
       </c>
       <c r="D534" t="inlineStr"/>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Сборка ходового мотора 00773605200600000</t>
+          <t>Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
@@ -14881,21 +14869,21 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1159901036</t>
+          <t>1990202279</t>
         </is>
       </c>
       <c r="B535" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Пружинная петля</t>
+          <t>Хомут спирального червяка</t>
         </is>
       </c>
       <c r="D535" t="inlineStr"/>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
+          <t>Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
@@ -14907,21 +14895,21 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1990200692</t>
+          <t>1990202282</t>
         </is>
       </c>
       <c r="B536" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Резиновая  лента  с  пластическим покрытием</t>
+          <t>Хомут спирального червяка</t>
         </is>
       </c>
       <c r="D536" t="inlineStr"/>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Cистема топлива 00773607100400000</t>
+          <t>Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
@@ -14933,11 +14921,11 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>1990202279</t>
+          <t>1990202287</t>
         </is>
       </c>
       <c r="B537" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
@@ -14947,7 +14935,7 @@
       <c r="D537" t="inlineStr"/>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Cистема отвода тепла 00773607100600000; Cистема топлива 00773607100400000</t>
+          <t>Cистема отвода тепла 00773607100600000</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
@@ -14959,11 +14947,11 @@
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1990202282</t>
+          <t>1990202288</t>
         </is>
       </c>
       <c r="B538" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
@@ -14973,7 +14961,7 @@
       <c r="D538" t="inlineStr"/>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Cистема отвода тепла 00773607100600000</t>
+          <t>Впускная система 00773607100800000</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
@@ -14985,11 +14973,11 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1990202287</t>
+          <t>1990202290</t>
         </is>
       </c>
       <c r="B539" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
@@ -14999,7 +14987,7 @@
       <c r="D539" t="inlineStr"/>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Cистема отвода тепла 00773607100600000</t>
+          <t>Впускная система 00773607100800000</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
@@ -15011,21 +14999,21 @@
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>1990202288</t>
+          <t>1990300401</t>
         </is>
       </c>
       <c r="B540" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Хомут спирального червяка</t>
+          <t>U-образная клейкая лента</t>
         </is>
       </c>
       <c r="D540" t="inlineStr"/>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Впускная система 00773607100800000</t>
+          <t>Башенная стрела в сборе 00773700400000000</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
@@ -15037,7 +15025,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>1990202290</t>
+          <t>1999904986</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -15045,13 +15033,13 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Хомут спирального червяка</t>
+          <t>Коробка для файлов</t>
         </is>
       </c>
       <c r="D541" t="inlineStr"/>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Впускная система 00773607100800000</t>
+          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
@@ -15063,80 +15051,28 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>1990300401</t>
+          <t>204050239</t>
         </is>
       </c>
       <c r="B542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>U-образная клейкая лента</t>
-        </is>
-      </c>
-      <c r="D542" t="inlineStr"/>
+          <t>Синтетическое трансмиссионное масло Mobil</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>SHC220-P20L(новый)</t>
+        </is>
+      </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Башенная стрела в сборе 00773700400000000</t>
+          <t>Шасси 00773602800000000</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
-        <is>
-          <t>ZA18J</t>
-        </is>
-      </c>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr">
-        <is>
-          <t>1999904986</t>
-        </is>
-      </c>
-      <c r="B543" t="n">
-        <v>2</v>
-      </c>
-      <c r="C543" t="inlineStr">
-        <is>
-          <t>Коробка для файлов</t>
-        </is>
-      </c>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr">
-        <is>
-          <t>Рабочая платформа 00773700100000000; Рабочая платформа 00773700110000000</t>
-        </is>
-      </c>
-      <c r="F543" t="inlineStr">
-        <is>
-          <t>ZA18J</t>
-        </is>
-      </c>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr">
-        <is>
-          <t>204050239</t>
-        </is>
-      </c>
-      <c r="B544" t="n">
-        <v>0</v>
-      </c>
-      <c r="C544" t="inlineStr">
-        <is>
-          <t>Синтетическое трансмиссионное масло Mobil</t>
-        </is>
-      </c>
-      <c r="D544" t="inlineStr">
-        <is>
-          <t>SHC220-P20L(новый)</t>
-        </is>
-      </c>
-      <c r="E544" t="inlineStr">
-        <is>
-          <t>Шасси 00773602800000000</t>
-        </is>
-      </c>
-      <c r="F544" t="inlineStr">
         <is>
           <t>ZA18J</t>
         </is>
